--- a/docs/tutorial-assets/workbooks/03_PyroApp_Optimization_Workflows.xlsx
+++ b/docs/tutorial-assets/workbooks/03_PyroApp_Optimization_Workflows.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_WORK\Code\Rust\pyroapp-docs\docs\tutorial-assets\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88F3B56-8798-4964-A503-A96FBC06DB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF17D71-302A-475D-8879-451AE0F23CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51720" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,12 +60,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="103">
   <si>
     <t>PyroApp Example 03 — Optimization Workflows (Ca-Zn-O)</t>
   </si>
   <si>
-    <t>Synthetic regression helpers plus the live derivative-matrix dependency pattern for an open DAT.</t>
+    <t>Synthetic regression helpers plus a deliberately gated live Ca-Zn-O derivative-matrix workflow.</t>
   </si>
   <si>
     <t>Before you calculate</t>
@@ -74,7 +74,7 @@
     <t>1. Install/load PyroApp in desktop Excel.</t>
   </si>
   <si>
-    <t>2. Download Ca-Zn-O.dat and place it beside this workbook.</t>
+    <t>2. Download Ca-Zn-O_optimization_working.dat and place it beside this workbook.</t>
   </si>
   <si>
     <t>3. Blue cells are inputs; black cells are formulas; purple cells are controls.</t>
@@ -86,19 +86,31 @@
     <t>Datafile</t>
   </si>
   <si>
+    <t>Ca-Zn-O_optimization_working.dat</t>
+  </si>
+  <si>
+    <t>Download DAT</t>
+  </si>
+  <si>
+    <t>Docs</t>
+  </si>
+  <si>
+    <t>PyroApp documentation</t>
+  </si>
+  <si>
+    <t>PyroApp status</t>
+  </si>
+  <si>
+    <t>Baseline DAT</t>
+  </si>
+  <si>
     <t>Ca-Zn-O.dat</t>
   </si>
   <si>
-    <t>Download DAT</t>
-  </si>
-  <si>
-    <t>Docs</t>
-  </si>
-  <si>
-    <t>PyroApp documentation</t>
-  </si>
-  <si>
-    <t>PyroApp status</t>
+    <t>Write safety</t>
+  </si>
+  <si>
+    <t>The live sheets use only the separately named working DAT. Enable DAT writes remains FALSE in the saved workbook.</t>
   </si>
   <si>
     <t>Synthetic linear-regression example</t>
@@ -155,7 +167,7 @@
     <t>Best 2-parameter mask</t>
   </si>
   <si>
-    <t>Convention: residual = target - current; A = d(current)/d(parameter); solve A Δp ≈ residual. Recalculate the real nonlinear model after applying a step.</t>
+    <t>Convention: residual = target - current; A = d(current)/d(parameter); solve A Δp ≈ residual. Recalculate the nonlinear model after a user-reviewed, damped step.</t>
   </si>
   <si>
     <t>Parameter range</t>
@@ -173,7 +185,7 @@
     <t>Live targets!$J$8:$J$12</t>
   </si>
   <si>
-    <t>Run PyroApp → Calculation → Calculate derivative matrix while this sheet is active. B1:B6 are reserved for the command.</t>
+    <t>Run PyroApp → Calculation → Calculate derivative matrix while this sheet is active. B1:B6 are reserved for the command. Set Enable DAT writes to TRUE only after confirming the disposable working DAT.</t>
   </si>
   <si>
     <t>Trigger cell</t>
@@ -224,13 +236,13 @@
     <t>Target 5</t>
   </si>
   <si>
-    <t>PyroApp perturbs numeric parameter cells, changes the trigger, waits for dependent SET/calculation formulas, writes derivative columns, then restores the original parameter vector.</t>
-  </si>
-  <si>
-    <t>Optimization parameter block</t>
-  </si>
-  <si>
-    <t>The starting numbers are the first Slag-liq ordinary G interaction terms in the supplied working DAT.</t>
+    <t>The command perturbs numeric parameter cells, changes the trigger once per state, waits for gated SET/calculation dependencies, writes derivative columns, then restores the original parameter vector. With Enable DAT writes = FALSE, it cannot alter the DAT.</t>
+  </si>
+  <si>
+    <t>Ca-Zn-O working-DAT parameter block</t>
+  </si>
+  <si>
+    <t>The interaction identity and initial values below come from the current Ca-Zn-O working DAT through the installed XLL.</t>
   </si>
   <si>
     <t>Phase</t>
@@ -239,7 +251,13 @@
     <t>Slag-liq</t>
   </si>
   <si>
-    <t>Interaction identity</t>
+    <t>Coefficient order</t>
+  </si>
+  <si>
+    <t>Interaction identity (first listed)</t>
+  </si>
+  <si>
+    <t>constant, T, T ln(T), T², T³, 1/T</t>
   </si>
   <si>
     <t>Parameter 1 constant</t>
@@ -263,6 +281,15 @@
     <t>Use p2?</t>
   </si>
   <si>
+    <t>Enable DAT writes</t>
+  </si>
+  <si>
+    <t>Current p1 (DAT read)</t>
+  </si>
+  <si>
+    <t>Current p2 (DAT read)</t>
+  </si>
+  <si>
     <t>Write p1</t>
   </si>
   <si>
@@ -272,13 +299,13 @@
     <t>Calculation token</t>
   </si>
   <si>
-    <t>These SET formulas modify the working DAT. Keep an untouched baseline copy.</t>
+    <t>Opening or recalculating the workbook does not call SET because Enable DAT writes is FALSE. For a deliberate derivative run, first use a fresh copy of Ca-Zn-O_optimization_working.dat, enable writes, run the Ribbon command, then set the gate back to FALSE.</t>
   </si>
   <si>
     <t>Live thermodynamic target template</t>
   </si>
   <si>
-    <t>Slag-liq is forced as the entered phase. Blue target G values are illustrative and must be replaced by real targets for research use.</t>
+    <t>Slag-liq is the entered phase. Blue target G values are illustrative and must be replaced by real measurements for research use.</t>
   </si>
   <si>
     <t>T, [C]</t>
@@ -296,6 +323,9 @@
     <t>ERROR</t>
   </si>
   <si>
+    <t>Residual = target - current</t>
+  </si>
+  <si>
     <t>Target G (illustrative)</t>
   </si>
   <si>
@@ -314,10 +344,10 @@
     <t>O</t>
   </si>
   <si>
-    <t>The target numbers are illustrative; the sheet teaches the live derivative dependency, not a Ca-Zn-O assessment.</t>
-  </si>
-  <si>
-    <t>Use the live derivative matrix</t>
+    <t>The residual sign is explicit: target minus current. ERROR = 0 permits a residual; any other status returns NA so a failed solve is not silently treated as zero.</t>
+  </si>
+  <si>
+    <t>Review the live derivative matrix</t>
   </si>
   <si>
     <t>d/dp1</t>
@@ -329,13 +359,16 @@
     <t>Best 1 parameter</t>
   </si>
   <si>
-    <t>Suggested p1</t>
-  </si>
-  <si>
-    <t>Suggested p2</t>
-  </si>
-  <si>
-    <t>Inspect and damp the proposed step before deliberately copying accepted values into Parameters. Do not create an automatic circular optimizer.</t>
+    <t>Damping α</t>
+  </si>
+  <si>
+    <t>Suggested p1 = current + αΔp</t>
+  </si>
+  <si>
+    <t>Suggested p2 = current + αΔp</t>
+  </si>
+  <si>
+    <t>Review and damp the proposed step before deliberately copying accepted values into Parameters. This workbook has no automatic circular optimizer and never changes parameter cells from its regression result.</t>
   </si>
 </sst>
 </file>
@@ -783,11 +816,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="102.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -910,6 +943,22 @@
       <c r="B14" s="1">
         <f>IFERROR(_xll.XLL_CA_VERSION(),"PyroApp not loaded")</f>
         <v>714</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -953,7 +1002,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -967,7 +1016,7 @@
     </row>
     <row r="2" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -981,24 +1030,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2">
         <v>25</v>
@@ -1015,7 +1064,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>-15</v>
@@ -1032,7 +1081,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2">
         <v>8</v>
@@ -1049,7 +1098,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2">
         <v>-6</v>
@@ -1066,7 +1115,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2">
         <v>120</v>
@@ -1083,7 +1132,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2">
         <v>-80</v>
@@ -1100,7 +1149,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -1110,13 +1159,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -1187,7 +1236,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C23" s="2" t="b">
         <v>1</v>
@@ -1201,7 +1250,7 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
@@ -1215,7 +1264,7 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1" cm="1">
         <f t="array" ref="C26:E26">_xll.XLL_LINEAR_REGRESSION($B$16:$D$21,$B$6:$B$11,$C$6:$C$11,$C$23:$E$23,$C$24:$E$24)</f>
@@ -1230,7 +1279,7 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C28" s="1" cm="1">
         <f t="array" ref="C28:E28">_xll.XLL_BEST_COMBINATION($B$16:$D$21,$B$6:$B$11,$C$6:$C$11,$C$23:$E$23,$C$24:$E$24,2)</f>
@@ -1516,7 +1565,7 @@
     </row>
     <row r="41" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -1553,13 +1602,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
@@ -1570,13 +1619,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
@@ -1587,10 +1636,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -1602,67 +1651,67 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C11" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C12" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -1686,17 +1735,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="90.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="16" width="18" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1710,7 +1761,7 @@
     </row>
     <row r="2" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -1724,20 +1775,26 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1" t="str" cm="1">
         <f t="array" ref="B5:B6">_xll.XLL_CA_LIST_INTERACTIONS_G(Start!$B$10,$B$4)</f>
         <v>(Ca)^[0]-(Zn)^[0]: (O) (Quasichemical)</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" t="str">
@@ -1746,23 +1803,23 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B8" s="2">
-        <v>-119160.32000000001</v>
+        <v>-26652.080000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B9" s="2">
-        <v>21.673120000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B10" s="2">
         <v>100</v>
@@ -1770,7 +1827,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2">
         <v>0.1</v>
@@ -1778,7 +1835,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B12" s="5">
         <v>0</v>
@@ -1786,7 +1843,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B13" s="5" t="b">
         <v>1</v>
@@ -1794,53 +1851,81 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B14" s="5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="1" cm="1">
+        <f t="array" ref="B17">_xll.XLL_CA_GET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$4,$B$5,1)</f>
+        <v>-26652.080000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="1" t="str">
-        <f>_xll.XLL_CA_SET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$4,$B$5,1,$B$8,$B$12)</f>
-        <v>#PYROAPP_ERROR: InvalidOperationException:Invalid DAT request: interaction value index must be 1..6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="1" t="str">
-        <f>_xll.XLL_CA_SET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$4,$B$5,2,$B$9,$B$12)</f>
-        <v>#PYROAPP_ERROR: InvalidOperationException:Invalid DAT request: interaction value index must be 1..6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+      <c r="B18" s="1" cm="1">
+        <f t="array" ref="B18">_xll.XLL_CA_GET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$4,$B$5,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <f>IF($B$15,_xll.XLL_CA_SET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$4,$B$5,$B$8,1,$B$12),"Disabled")</f>
+        <v>Disabled</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="1">
-        <f>IF(AND(B18&lt;&gt;"",B19&lt;&gt;""),B12,B12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+        <v>77</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <f>IF($B$15,_xll.XLL_CA_SET_INTERACTION_PARAMETERS_G(Start!$B$10,$B$4,$B$5,$B$9,2,$B$12),"Disabled")</f>
+        <v>Disabled</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="1">
+        <f>B12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1860,7 +1945,7 @@
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
@@ -1869,7 +1954,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="9" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1883,7 +1968,7 @@
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -1897,83 +1982,83 @@
     </row>
     <row r="4" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B5" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B6" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -1993,14 +2078,14 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" cm="1">
-        <f t="array" ref="H8:I12">_xll.XLL_CA_CALCULATE(Start!$B$10,$B$4:$F$6,$B$8:$F$12,$H$4:$I$6,$M$5:$M$5,Parameters!$B$21)</f>
+        <f t="array" ref="H8:I12">_xll.XLL_CA_CALCULATE(Start!$B$10,$B$4:$F$6,$B$8:$F$12,$H$4:$I$6,$M$5:$M$5,Parameters!$B$23)</f>
         <v>-699151.3245521005</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <f>IF(I8=0,K8-H8,0)</f>
+        <f>IF(I8=0,K8-H8,NA())</f>
         <v>-100848.6754478995</v>
       </c>
       <c r="K8" s="2">
@@ -2030,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <f>IF(I9=0,K9-H9,0)</f>
+        <f>IF(I9=0,K9-H9,NA())</f>
         <v>-188413.14233741153</v>
       </c>
       <c r="K9" s="2">
@@ -2060,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <f>IF(I10=0,K10-H10,0)</f>
+        <f>IF(I10=0,K10-H10,NA())</f>
         <v>-280871.25919732638</v>
       </c>
       <c r="K10" s="2">
@@ -2090,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <f>IF(I11=0,K11-H11,0)</f>
+        <f>IF(I11=0,K11-H11,NA())</f>
         <v>-380074.37636658561</v>
       </c>
       <c r="K11" s="2">
@@ -2120,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <f>IF(I12=0,K12-H12,0)</f>
+        <f>IF(I12=0,K12-H12,NA())</f>
         <v>71243.264764937223</v>
       </c>
       <c r="K12" s="2">
@@ -2129,7 +2214,7 @@
     </row>
     <row r="15" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2155,10 +2240,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="16" width="18" customWidth="1"/>
@@ -2166,7 +2251,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="9" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2180,16 +2265,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -2279,7 +2364,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B12" s="2" t="b">
         <v>1</v>
@@ -2290,7 +2375,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
@@ -2301,7 +2386,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" cm="1">
         <f t="array" ref="B15:C15">_xll.XLL_LINEAR_REGRESSION($C$5:$D$9,$B$5:$B$9,$A$5:$A$9,$B$12:$C$12,$B$13:$C$13)</f>
@@ -2313,7 +2398,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B17" s="1" cm="1">
         <f t="array" ref="B17:C17">_xll.XLL_BEST_COMBINATION($C$5:$D$9,$B$5:$B$9,$A$5:$A$9,$B$12:$C$12,$B$13:$C$13,1)</f>
@@ -2325,38 +2410,46 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="1">
-        <f>Parameters!B8+B15</f>
-        <v>-119160.32000000001</v>
+        <v>99</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.25</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B21" s="1">
-        <f>Parameters!B9+C15</f>
-        <v>21.673120000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
+        <f>Parameters!B8+$B$20*B15</f>
+        <v>-26652.080000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="1">
+        <f>Parameters!B9+$B$20*C15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
